--- a/metadata_experiment/data/index_catalog.xlsx
+++ b/metadata_experiment/data/index_catalog.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>贫困生计 | 死亡苦难</t>
+          <t>其他/未分类</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>地 | 苦</t>
+          <t>作家 | 写作 | 地 | 苦 | 前言</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -520,12 +520,12 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>死亡苦难 | 贫困生计 | 家珍病逝 | 活着信念</t>
+          <t>序言与创作背景</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>死 | 地 | 苦 | 命</t>
+          <t>作家 | 死 | 老黑奴 | 地 | 苦 | 命</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -555,12 +555,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>贫困生计 | 活着信念 | 死亡苦难 | 家庭生活</t>
+          <t>序言与创作背景</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>田 | 活着 | 地 | 苦 | 娘 | 干活</t>
+          <t>田 | 地 | 苦 | 老黑奴 | 娘 | 干活 | 写作</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -590,7 +590,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>贫困生计 | 死亡苦难</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>老牛陪伴 | 贫困生计 | 活着信念</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 老牛陪伴 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 凤霞经历 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>家庭生活 | 赌博败家 | 贫困生计 | 有庆经历</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 死亡苦难 | 赌博败家</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -820,7 +820,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>贫困生计 | 家珍病逝 | 死亡苦难 | 家庭生活</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 死亡苦难</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>家庭生活 | 赌博败家 | 贫困生计 | 土地改革</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>赌博败家 | 土地改革 | 贫困生计</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>赌博败家 | 土地改革 | 家庭生活 | 家珍病逝</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 赌博败家</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>赌博败家 | 土地改革 | 家庭生活 | 贫困生计</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>贫困生计 | 赌博败家 | 土地改革 | 死亡苦难</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 死亡苦难 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 死亡苦难 | 凤霞经历</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 死亡苦难 | 活着信念</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>家庭生活 | 死亡苦难 | 家珍病逝 | 赌博败家</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 死亡苦难 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 赌博败家 | 土地改革</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 死亡苦难</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 凤霞经历 | 贫困生计</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 贫困生计 | 老牛陪伴</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 土地改革 | 赌博败家</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 赌博败家 | 土地改革</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 死亡苦难 | 家珍病逝</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>家庭生活 | 赌博败家 | 土地改革 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 有庆经历</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 有庆经历</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1879,7 +1879,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>参军战争 | 死亡苦难 | 家珍病逝 | 家庭生活</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>贫困生计 | 参军战争 | 死亡苦难 | 家庭生活</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>贫困生计 | 家珍病逝 | 死亡苦难 | 春生经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>贫困生计 | 家珍病逝 | 死亡苦难 | 活着信念</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>贫困生计 | 死亡苦难 | 家珍病逝 | 家庭生活</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>贫困生计 | 春生经历 | 参军战争 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>贫困生计 | 春生经历 | 死亡苦难 | 家庭生活</t>
+          <t>贫困生计 | 死亡苦难</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>贫困生计 | 家珍病逝 | 死亡苦难 | 家庭生活</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 家珍 | 凤霞 | 有庆 | 活着 | 娘</t>
+          <t>死 | 地 | 春生 | 家珍 | 凤霞 | 有庆 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2194,12 +2194,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>贫困生计 | 死亡苦难 | 家珍病逝 | 春生经历</t>
+          <t>死亡苦难</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 血 | 苦 | 活着 | 命</t>
+          <t>死 | 地 | 春生 | 血 | 苦 | 命</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>死亡苦难 | 家珍病逝 | 贫困生计 | 春生经历</t>
+          <t>死亡苦难 | 活着信念</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>贫困生计 | 参军战争 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>地 | 死 | 解放军 | 春生 | 大炮 | 活着 | 命</t>
+          <t>地 | 死 | 解放军 | 春生 | 大炮 | 命</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>贫困生计 | 参军战争 | 死亡苦难 | 家庭生活</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 有庆经历 | 参军战争</t>
+          <t>家庭生活 | 贫困生计</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 死亡苦难</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>土地改革 | 赌博败家 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计 | 赌博败家</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>家珍病逝 | 老牛陪伴 | 死亡苦难 | 家庭生活</t>
+          <t>活着信念</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>家庭生活 | 老牛陪伴 | 凤霞经历 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 凤霞经历 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>有庆经历 | 家庭生活 | 凤霞经历 | 贫困生计</t>
+          <t>家庭生活 | 贫困生计</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 有庆经历</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 贫困生计</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 家珍病逝 | 贫困生计</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>贫困生计 | 人民公社 | 家庭生活 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>人民公社 | 家庭生活 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 人民公社 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>人民公社 | 家庭生活 | 家珍病逝 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>人民公社 | 家庭生活 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>家庭生活 | 人民公社 | 贫困生计 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>家珍病逝 | 家庭生活 | 贫困生计 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 家珍病逝 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 贫困生计 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>家珍病逝 | 家庭生活 | 死亡苦难 | 人民公社</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>家珍病逝 | 家庭生活 | 人民公社 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 人民公社 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 死亡苦难 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 家珍病逝 | 参军战争</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 贫困生计</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 贫困生计 | 凤霞经历</t>
+          <t>贫困生计 | 死亡苦难</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 家珍病逝 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 有庆经历 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 家珍病逝 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 凤霞经历 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 人民公社 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 家珍病逝 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 家珍病逝 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 人民公社 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>家珍病逝 | 家庭生活 | 死亡苦难 | 有庆经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>有庆经历 | 家庭生活 | 医疗献血 | 贫困生计</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>有庆经历 | 家庭生活 | 医疗献血 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>有庆经历 | 家庭生活 | 医疗献血 | 死亡苦难</t>
+          <t>死亡苦难 | 家庭生活</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>春生经历 | 死亡苦难 | 医疗献血 | 家珍病逝</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>家庭生活 | 死亡苦难 | 家珍病逝 | 有庆经历</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>家庭生活 | 有庆经历 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 有庆经历 | 死亡苦难</t>
+          <t>家庭生活 | 贫困生计</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 家珍病逝 | 有庆经历</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>家珍病逝 | 家庭生活 | 医疗献血 | 死亡苦难</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 死亡苦难 | 贫困生计</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 凤霞经历 | 死亡苦难</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>春生经历 | 家珍病逝 | 家庭生活 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 凤霞经历 | 春生经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 贫困生计 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 人民公社</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 凤霞经历 | 人民公社</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 贫困生计</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 二喜苦根</t>
+          <t>家庭生活 | 贫困生计</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 家珍病逝</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 二喜苦根</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 贫困生计</t>
+          <t>家庭生活 | 贫困生计</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 贫困生计 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 贫困生计</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 人民公社 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>人民公社 | 贫困生计 | 土地改革 | 春生经历</t>
+          <t>其他/未分类</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>人民公社 | 贫困生计 | 春生经历 | 家庭生活</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>春生经历 | 家珍病逝 | 家庭生活 | 贫困生计</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>春生经历 | 家庭生活 | 家珍病逝 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 死 | 命 | 活着 | 凤霞 | 有庆 | 爹</t>
+          <t>春生 | 家珍 | 死 | 命 | 凤霞 | 有庆 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 家珍病逝 | 二喜苦根</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 家珍病逝</t>
+          <t>家庭生活</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>凤霞经历 | 家庭生活 | 二喜苦根 | 贫困生计</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 死亡苦难</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>家庭生活 | 凤霞经历 | 二喜苦根 | 家珍病逝</t>
+          <t>贫困生计 | 家庭生活</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 凤霞经历 | 死亡苦难</t>
+          <t>贫困生计 | 家珍病逝</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>家庭生活 | 家珍病逝 | 死亡苦难 | 凤霞经历</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>家庭生活 | 死亡苦难 | 家珍病逝 | 二喜苦根</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>家庭生活 | 二喜苦根 | 死亡苦难 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>家庭生活 | 二喜苦根 | 凤霞经历 | 死亡苦难</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>二喜苦根 | 家庭生活 | 死亡苦难 | 凤霞经历</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>家庭生活 | 死亡苦难 | 二喜苦根 | 凤霞经历</t>
+          <t>死亡苦难 | 活着信念</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>家庭生活 | 二喜苦根 | 死亡苦难 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>死亡苦难 | 家庭生活 | 二喜苦根 | 贫困生计</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>家庭生活 | 贫困生计 | 死亡苦难 | 二喜苦根</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>家庭生活 | 死亡苦难 | 二喜苦根 | 老牛陪伴</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>死亡苦难 | 二喜苦根 | 家庭生活 | 家珍病逝</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>死亡苦难 | 二喜苦根 | 家庭生活 | 家珍病逝</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>老牛陪伴 | 贫困生计 | 死亡苦难 | 家珍病逝</t>
+          <t>贫困生计 | 活着信念</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>老牛陪伴 | 家庭生活 | 贫困生计 | 凤霞经历</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>贫困生计 | 家庭生活 | 凤霞经历 | 二喜苦根</t>
+          <t>贫困生计</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">

--- a/metadata_experiment/data/index_catalog.xlsx
+++ b/metadata_experiment/data/index_catalog.xlsx
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Topics</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Characters</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Topics</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -482,15 +482,15 @@
       <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>其他/未分类</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>作家 | 写作 | 地 | 苦 | 前言</t>
+          <t>作家 | 写作 | 作者 | 作品 | 前言</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,15 +517,15 @@
       <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>序言与创作背景</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>作家 | 死 | 老黑奴 | 地 | 苦 | 命</t>
+          <t>作家 | 作品 | 老黑奴 | 命</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,15 +552,15 @@
       <c r="C4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>序言与创作背景</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>田 | 地 | 苦 | 老黑奴 | 娘 | 干活 | 写作</t>
+          <t>活着 | 老黑奴 | 娘 | 孩子 | 写作 | 作品</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -587,15 +587,15 @@
       <c r="C5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>地 | 哭 | 田</t>
+          <t>孩子</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>福贵</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>牛 | 田 | 地 | 老牛 | 命</t>
+          <t>老牛 | 耕田 | 田地 | 命</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>地 | 牛 | 田 | 爹 | 二喜 | 家珍 | 凤霞 | 有庆</t>
+          <t>爹 | 耕田 | 二喜 | 田产 | 有庆 | 凤霞 | 家珍 | 苦根</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>爹 | 地 | 凤霞 | 家珍 | 穷 | 田 | 米</t>
+          <t>爹 | 凤霞 | 田地 | 家珍 | 穷</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>有庆 | 爹 | 赌博 | 家珍 | 凤霞 | 地 | 娘 | 日子</t>
+          <t>爹 | 赌博 | 有庆 | 凤霞 | 家珍 | 回家 | 娘 | 日子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -780,22 +780,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>爹 | 病 | 家珍 | 有庆 | 娘 | 赌博 | 凤霞 | 地</t>
+          <t>爹 | 娘 | 赌博 | 有庆 | 家珍 | 凤霞 | 日子</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -817,20 +817,20 @@
       <c r="C11" t="n">
         <v>15</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>赌博败家</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>病 | 爹 | 米 | 地 | 死</t>
+          <t>爹 | 回家</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>家珍</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>家珍 | 地 | 娘 | 爹 | 死 | 日子</t>
+          <t>家珍 | 娘 | 爹 | 日子</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>龙二 | 家珍 | 地 | 爹 | 赌博 | 娘 | 凤霞</t>
+          <t>龙二 | 爹 | 赌博 | 家珍 | 娘 | 骰子 | 凤霞 | 说话</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -935,17 +935,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>龙二</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>龙二 | 赌博 | 地</t>
+          <t>龙二 | 赌博</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>家珍 | 有庆 | 龙二</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>龙二 | 家珍 | 地 | 赌博 | 有庆 | 娘 | 哭</t>
+          <t>龙二 | 家珍 | 骰子 | 赌博 | 娘 | 有庆 | 说话</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>家珍 | 有庆 | 龙二</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>家珍 | 龙二 | 地 | 有庆 | 爹 | 死 | 米 | 上学</t>
+          <t>家珍 | 龙二 | 爹 | 有庆 | 上学 | 说话</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>家珍 | 有庆 | 龙二</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>龙二 | 家珍 | 地 | 有庆 | 米 | 娘 | 上学 | 命</t>
+          <t>龙二 | 骰子 | 家珍 | 有庆 | 上学 | 回家 | 娘 | 命</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>龙二</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>龙二 | 地 | 死 | 家产 | 穷 | 米 | 苦</t>
+          <t>龙二 | 输光 | 骰子 | 家产 | 穷</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>死 | 家珍 | 娘 | 爹 | 地 | 哭 | 家产 | 有庆</t>
+          <t>娘 | 爹 | 家珍 | 家产 | 输光 | 回家 | 有庆 | 穷</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>爹 | 凤霞 | 地 | 哭 | 家珍 | 娘 | 死 | 穷</t>
+          <t>爹 | 娘 | 凤霞 | 家珍 | 说话 | 孩子 | 穷 | 命</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>福贵</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>爹 | 地 | 娘 | 死 | 命 | 穷 | 苦</t>
+          <t>爹 | 娘 | 命 | 穷</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>哭 | 爹 | 龙二 | 凤霞 | 死 | 家珍 | 娘 | 地</t>
+          <t>爹 | 龙二 | 回家 | 凤霞 | 娘 | 血 | 家珍 | 没钱</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1287,17 +1287,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>爹 | 地 | 家珍 | 娘 | 凤霞 | 牛 | 哭 | 穷</t>
+          <t>爹 | 娘 | 家珍 | 凤霞 | 吃饭 | 回家 | 穷 | 没钱</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>龙二</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>爹 | 龙二 | 地 | 死 | 牛 | 娘 | 田 | 哭</t>
+          <t>爹 | 龙二 | 娘</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>爹 | 家珍 | 地 | 凤霞 | 娘 | 哭 | 死 | 苦</t>
+          <t>爹 | 家珍 | 娘 | 凤霞 | 断气 | 命</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1406,22 +1406,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>家珍 | 爹 | 娘 | 地 | 死 | 凤霞 | 穷 | 坟</t>
+          <t>家珍 | 爹 | 娘 | 凤霞 | 穷</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 娘 | 爹 | 地 | 哭 | 死 | 命</t>
+          <t>家珍 | 凤霞 | 娘 | 爹 | 孩子 | 命</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>凤霞 | 地 | 日子 | 爹 | 老牛 | 牛</t>
+          <t>凤霞 | 日子 | 老牛 | 爹</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 地 | 娘 | 爹 | 苦</t>
+          <t>凤霞 | 家珍 | 娘 | 爹 | 孩子</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>龙二 | 娘 | 地 | 凤霞 | 穷 | 田 | 爹 | 地主</t>
+          <t>龙二 | 娘 | 凤霞 | 穷 | 地主 | 爹 | 日子</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1604,22 +1604,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>龙二 | 娘 | 田 | 地 | 凤霞 | 病 | 穷 | 干活</t>
+          <t>龙二 | 娘 | 血 | 凤霞 | 穷 | 一家人</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>凤霞 | 地 | 死 | 娘 | 病 | 田 | 日子 | 龙二</t>
+          <t>娘 | 凤霞 | 日子 | 龙二 | 家产 | 输光 | 血 | 一辈子</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞 | 龙二</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>龙二 | 凤霞 | 娘 | 苦 | 地 | 死 | 日子 | 赌场</t>
+          <t>龙二 | 凤霞 | 娘 | 日子 | 赌场 | 一辈子</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 龙二</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 娘 | 龙二 | 凤霞 | 地 | 赌场 | 爹</t>
+          <t>家珍 | 娘 | 龙二 | 有庆 | 凤霞 | 赌场 | 爹 | 孩子</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1761,17 +1761,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 娘 | 有庆 | 田 | 地 | 穷 | 干活</t>
+          <t>家珍 | 娘 | 凤霞 | 有庆 | 穷 | 孩子</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 娘 | 地 | 田 | 凤霞 | 病 | 苦</t>
+          <t>家珍 | 娘 | 有庆 | 日子 | 凤霞 | 说话 | 爹 | 孩子</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 地 | 死 | 有庆 | 爹 | 娘 | 田</t>
+          <t>凤霞 | 家珍 | 国民党 | 大炮 | 有庆 | 爹 | 娘 | 孩子</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1876,20 +1876,20 @@
       <c r="C38" t="n">
         <v>46</v>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>赌博败家</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>死 | 大炮 | 娘 | 地 | 血 | 壮丁 | 国民党 | 哭</t>
+          <t>大炮 | 娘 | 壮丁 | 国民党 | 血</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1914,17 +1914,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>参军战争</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>家珍 | 老全</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>赌博败家</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>地 | 大炮 | 哭 | 家珍 | 死 | 命 | 娘 | 田</t>
+          <t>老全 | 大炮 | 命 | 壮丁 | 当兵 | 田地 | 血 | 家珍</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1954,22 +1954,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>参军战争</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>春生 | 老全</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 娘 | 大炮 | 命</t>
+          <t>老全 | 春生 | 大炮 | 娘 | 孩子 | 命</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>春生 | 老全</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>死 | 地 | 命 | 米 | 春生 | 赌钱 | 粮食 | 血</t>
+          <t>老全 | 命 | 春生 | 赌钱 | 解放军 | 粮食 | 血 | 说话</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>参军战争</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>老全</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>地 | 米 | 死 | 娘 | 饿 | 埋 | 坟 | 命</t>
+          <t>老全 | 娘 | 饿 | 命</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>春生 | 老全</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>春生 | 地 | 米 | 大炮 | 死 | 苦 | 命 | 日子</t>
+          <t>春生 | 老全 | 大炮 | 命 | 日子</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2110,17 +2110,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>春生 | 老全</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>贫困生计 | 死亡苦难</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>地 | 春生 | 死 | 哭 | 娘 | 饿 | 大炮 | 日子</t>
+          <t>春生 | 老全 | 大炮 | 娘 | 孩子 | 饿 | 日子 | 一辈子</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2149,22 +2149,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 春生 | 老全</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 家珍 | 凤霞 | 有庆 | 娘 | 饿</t>
+          <t>说话 | 老全 | 春生 | 活着 | 有庆 | 凤霞 | 家珍 | 娘</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2189,22 +2189,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>春生 | 老全</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>死亡苦难</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 血 | 苦 | 命</t>
+          <t>老全 | 春生 | 血 | 说话 | 活着 | 命</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>家珍 | 春生 | 老全</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>死亡苦难 | 活着信念</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>死 | 地 | 春生 | 哭 | 家珍 | 娘 | 苦 | 米</t>
+          <t>春生 | 老全 | 娘 | 家珍 | 孩子 | 命</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2268,22 +2268,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>春生</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>地 | 死 | 解放军 | 春生 | 大炮 | 命</t>
+          <t>解放军 | 春生 | 孩子 | 大炮 | 活着 | 命</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2307,17 +2307,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>参军战争</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>家珍</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>地 | 解放军 | 哭 | 家珍 | 饿 | 死 | 娘 | 命</t>
+          <t>回家 | 解放军 | 饿 | 家珍 | 说话 | 娘 | 命</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>家庭生活 | 贫困生计</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>凤霞 | 有庆 | 解放军 | 家珍 | 地 | 爹 | 死 | 娘</t>
+          <t>凤霞 | 有庆 | 解放军 | 家珍 | 爹 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2387,22 +2387,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 龙二</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>家珍 | 地 | 凤霞 | 有庆 | 娘 | 死 | 哭 | 龙二</t>
+          <t>家珍 | 娘 | 有庆 | 凤霞 | 龙二 | 爹 | 孩子 | 赌钱</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>土地改革与龙二</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 龙二</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>贫困生计 | 赌博败家</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>龙二 | 死 | 地 | 家珍 | 地主 | 枪毙 | 五枪 | 田产</t>
+          <t>龙二 | 地主 | 枪毙 | 五枪 | 田产 | 土地改革 | 家珍 | 回家</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2465,22 +2465,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>参军战争</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 龙二</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>活着信念</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>家珍 | 龙二 | 死 | 牛 | 地 | 命 | 病 | 爹</t>
+          <t>龙二 | 家珍 | 命 | 战场 | 五枪 | 一家人 | 爹</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2504,17 +2504,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 有庆 | 牛 | 田 | 地 | 苦 | 干活</t>
+          <t>凤霞 | 家珍 | 有庆 | 老牛 | 回家 | 饿 | 日子</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 苦 | 田 | 地 | 死 | 娘</t>
+          <t>凤霞 | 家珍 | 有庆 | 说话 | 上学 | 送人 | 娘 | 孩子</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2582,17 +2582,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 田 | 干活 | 地 | 哭 | 爹</t>
+          <t>凤霞 | 家珍 | 有庆 | 爹</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 上学 | 哭 | 娘 | 地 | 爹</t>
+          <t>有庆 | 凤霞 | 家珍 | 上学 | 娘 | 吃饭 | 爹 | 日子</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>家庭生活 | 贫困生计</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>有庆 | 上学 | 凤霞 | 家珍 | 地 | 爹 | 死 | 娘</t>
+          <t>上学 | 有庆 | 凤霞 | 孩子 | 家珍 | 吃饭 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 哭 | 地 | 爹 | 干活 | 牛</t>
+          <t>凤霞 | 家珍 | 有庆 | 爹</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2739,17 +2739,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 地 | 哭 | 上学 | 死 | 娘</t>
+          <t>凤霞 | 家珍 | 有庆 | 上学 | 孩子 | 吃饭 | 回家 | 娘</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2778,22 +2778,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 死 | 上学 | 田 | 地 | 饿</t>
+          <t>有庆 | 家珍 | 上学 | 凤霞 | 孩子 | 回家 | 饿 | 吃饭</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>有庆 | 地 | 田 | 队长 | 家珍 | 公社 | 凤霞 | 上学</t>
+          <t>队长 | 人民公社 | 公社 | 有庆 | 孩子 | 上学 | 家珍 | 当兵</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 食堂 | 队长 | 地 | 凤霞 | 饿 | 米</t>
+          <t>食堂 | 队长 | 有庆 | 家珍 | 饿 | 人民公社 | 公社 | 凤霞</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>人民公社与饥荒</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 队长 | 地 | 公社 | 凤霞 | 日子 | 爹</t>
+          <t>有庆 | 队长 | 公社 | 人民公社 | 挨饿 | 家珍 | 回家 | 孩子</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2937,17 +2937,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 队长</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 地 | 哭 | 家产 | 爹 | 公社 | 日子</t>
+          <t>队长 | 家珍 | 家产 | 人民公社 | 公社 | 爹 | 日子</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>人民公社与饥荒</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>家珍 | 队长</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>队长 | 家珍 | 地 | 娘 | 公社 | 死 | 哭 | 食堂</t>
+          <t>队长 | 家珍 | 人民公社 | 公社 | 娘 | 食堂 | 一家人 | 吃饭</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>有庆 | 队长 | 家珍 | 地 | 病 | 田 | 死 | 娘</t>
+          <t>队长 | 有庆 | 家珍 | 吃饭 | 娘 | 孩子</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3055,22 +3055,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>家珍 | 病 | 凤霞 | 地 | 田 | 有庆 | 队长 | 日子</t>
+          <t>家珍 | 队长 | 凤霞 | 日子 | 公社 | 食堂 | 有庆 | 孩子</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3094,17 +3094,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 地 | 病 | 爹 | 田 | 公社</t>
+          <t>有庆 | 家珍 | 凤霞 | 孩子 | 人民公社 | 公社 | 回家 | 爹</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3133,17 +3133,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 地 | 凤霞 | 公社</t>
+          <t>家珍 | 有庆 | 凤霞 | 孩子 | 人民公社 | 公社 | 回家</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3172,22 +3172,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 龙二 | 队长</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>家珍 | 病 | 凤霞 | 队长 | 医院 | 地 | 龙二 | 娘</t>
+          <t>家珍 | 队长 | 凤霞 | 龙二 | 回家 | 软骨病 | 娘</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>家珍 | 病 | 队长 | 凤霞 | 有庆 | 娘 | 地 | 食堂</t>
+          <t>家珍 | 队长 | 有庆 | 凤霞 | 食堂 | 软骨病 | 吃饭 | 回家</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3251,22 +3251,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 队长 | 病 | 凤霞 | 田 | 地 | 粮食</t>
+          <t>队长 | 家珍 | 有庆 | 食堂 | 粮食 | 凤霞 | 熬 | 公社</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3290,22 +3290,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 病 | 凤霞 | 地 | 田 | 死 | 血</t>
+          <t>家珍 | 有庆 | 凤霞 | 孩子 | 队长 | 血 | 回家 | 一辈子</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 国民党 | 病 | 爹 | 凤霞 | 死 | 地</t>
+          <t>有庆 | 国民党 | 孩子 | 家珍 | 爹 | 说话 | 凤霞</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3369,22 +3369,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 地 | 国民党 | 病 | 死 | 哭</t>
+          <t>有庆 | 家珍 | 说话 | 国民党 | 孩子 | 食堂 | 凤霞 | 送人</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>有庆 | 爹 | 地 | 家珍 | 田 | 跑步</t>
+          <t>有庆 | 孩子 | 爹 | 家珍 | 跑步 | 回家 | 说话</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>有庆</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>有庆 | 爹 | 地 | 跑步</t>
+          <t>有庆 | 孩子 | 爹 | 跑步 | 回家</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>贫困生计 | 死亡苦难</t>
-        </is>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 跑步 | 爹 | 娘 | 田 | 地</t>
+          <t>有庆 | 跑步 | 凤霞 | 家珍 | 回家 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3526,22 +3526,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>家珍 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 死 | 粮食 | 米 | 饿 | 队长 | 田</t>
+          <t>粮食 | 有庆 | 队长 | 家珍 | 饿 | 孩子 | 熬 | 公社</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3565,17 +3565,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 地 | 爹 | 娘 | 饿 | 米 | 哭</t>
+          <t>有庆 | 家珍 | 爹 | 孩子 | 挨饿 | 娘 | 饿 | 粮食</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3604,17 +3604,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>有庆 | 米 | 家珍 | 爹 | 地 | 苦 | 哭 | 命</t>
+          <t>有庆 | 爹 | 家珍 | 回家 | 孩子 | 命</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 地 | 病 | 米 | 队长 | 死 | 粮食</t>
+          <t>家珍 | 有庆 | 队长 | 粮食 | 挨饿 | 饿 | 日子 | 凤霞</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3682,17 +3682,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>凤霞 | 地 | 有庆 | 家珍 | 饿 | 爹 | 娘 | 田</t>
+          <t>凤霞 | 饿 | 有庆 | 说话 | 家珍 | 壮丁 | 田地 | 爹</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>凤霞婚育身亡</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 队长</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>凤霞 | 地 | 队长 | 命 | 田 | 家珍 | 死 | 爹</t>
+          <t>队长 | 凤霞 | 命 | 家珍 | 一家人 | 说话 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3760,17 +3760,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 有庆 | 米 | 地 | 爹 | 田 | 命</t>
+          <t>家珍 | 凤霞 | 有庆 | 爹 | 一家人 | 回家 | 命 | 孩子</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 米 | 地 | 队长 | 凤霞 | 熬 | 爹</t>
+          <t>家珍 | 队长 | 有庆 | 说话 | 熬 | 凤霞 | 一家人 | 爹</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3839,17 +3839,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 凤霞 | 米 | 日子 | 有庆 | 病 | 熬</t>
+          <t>家珍 | 队长 | 凤霞 | 日子 | 说话 | 熬 | 有庆 | 血</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3878,22 +3878,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>家珍 | 死 | 有庆 | 凤霞 | 病 | 地 | 埋 | 苦</t>
+          <t>家珍 | 有庆 | 凤霞 | 身子 | 活着 | 日子</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>有庆 | 血 | 地 | 医院 | 家珍 | 献血 | 病 | 医生</t>
+          <t>血 | 有庆 | 孩子 | 献血 | 血型 | 县长 | 家珍 | 命</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3958,17 +3958,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>有庆</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>有庆 | 血 | 抽血 | 死 | 医生 | 医院 | 爹 | 地</t>
+          <t>有庆 | 血 | 抽血 | 孩子 | 县长 | 爹 | 上学 | 血型</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>死亡苦难 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>有庆 | 医生 | 死 | 哭 | 家珍 | 地 | 抽血 | 病</t>
+          <t>有庆 | 活着 | 上学 | 抽血 | 血 | 家珍</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>春生文革与自杀</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>福贵 | 有庆 | 春生 | 老全</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>死 | 县长 | 春生 | 有庆 | 医生 | 地 | 哭 | 抽血</t>
+          <t>县长 | 春生 | 有庆 | 老全 | 命 | 抽血 | 血</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4076,17 +4076,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 有庆 | 春生 | 老全</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>有庆 | 死 | 春生 | 家珍 | 哭 | 爹 | 娘 | 田</t>
+          <t>春生 | 有庆 | 家珍 | 老全 | 爹 | 娘 | 上学 | 说话</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4115,22 +4115,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 死 | 埋 | 凤霞 | 医院 | 病 | 坟</t>
+          <t>有庆 | 家珍 | 说话 | 日子 | 上学 | 凤霞 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4154,22 +4154,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>家庭生活 | 贫困生计</t>
-        </is>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 死 | 坟 | 凤霞 | 地 | 埋 | 娘</t>
+          <t>家珍 | 有庆 | 凤霞 | 说话 | 娘 | 活着 | 日子</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4193,17 +4193,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 有庆</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 田 | 地 | 死 | 牛 | 坟 | 埋</t>
+          <t>家珍 | 有庆 | 做人 | 田地 | 耕田 | 说话</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4232,22 +4232,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>家珍 | 医生 | 病 | 凤霞 | 有庆 | 死 | 地 | 队长</t>
+          <t>家珍 | 队长 | 说话 | 日子 | 公社 | 有庆 | 凤霞 | 软骨病</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4271,22 +4271,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 队长</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 死 | 地 | 有庆 | 队长 | 哭 | 娘</t>
+          <t>家珍 | 凤霞 | 队长 | 有庆 | 娘 | 穷 | 日子 | 吃饭</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 病 | 地 | 死 | 有庆 | 娘 | 干活</t>
+          <t>家珍 | 凤霞 | 娘 | 有庆 | 回家 | 说话 | 饿 | 熬</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4349,22 +4349,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 春生 | 队长</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>家珍 | 春生 | 有庆 | 死 | 病 | 凤霞 | 队长 | 县长</t>
+          <t>春生 | 家珍 | 队长 | 有庆 | 县长 | 凤霞 | 解放军 | 回家</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4388,22 +4388,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 春生 | 队长</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 春生 | 队长 | 病 | 死 | 娘 | 命</t>
+          <t>家珍 | 凤霞 | 春生 | 队长 | 娘 | 命 | 文化大革命</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4427,17 +4427,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>凤霞</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>凤霞 | 娘 | 田 | 地 | 干活 | 苦 | 命</t>
+          <t>娘 | 凤霞 | 命</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4466,22 +4466,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 二喜 | 队长</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 队长 | 死 | 二喜 | 地 | 娘 | 田</t>
+          <t>凤霞 | 队长 | 家珍 | 二喜 | 说话 | 娘 | 做人</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4506,17 +4506,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 二喜 | 队长</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>家珍 | 二喜 | 凤霞 | 队长 | 娘 | 地 | 死 | 哭</t>
+          <t>家珍 | 二喜 | 队长 | 凤霞 | 娘 | 说话 | 爹 | 穷</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 二喜 | 队长</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 穷 | 地 | 田 | 队长 | 苦</t>
+          <t>二喜 | 家珍 | 穷 | 凤霞 | 队长 | 耕田 | 说话</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 干活 | 穷</t>
+          <t>二喜 | 家珍 | 凤霞 | 吃饭 | 穷</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4625,17 +4625,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>家庭生活 | 贫困生计</t>
-        </is>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 地 | 爹 | 娘 | 干活 | 苦</t>
+          <t>二喜 | 家珍 | 凤霞 | 爹 | 娘 | 说话 | 命</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4664,17 +4664,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>家庭日常生活</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 爹 | 娘</t>
+          <t>二喜 | 凤霞 | 家珍 | 送人 | 爹 | 娘 | 孩子</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>凤霞婚育身亡</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>凤霞 | 二喜 | 家珍 | 哭 | 娘 | 地 | 爹 | 干活</t>
+          <t>二喜 | 凤霞 | 家珍 | 娘 | 爹</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4742,17 +4742,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 二喜</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>家庭生活 | 贫困生计</t>
-        </is>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 二喜 | 地 | 有庆 | 干活 | 娘 | 田</t>
+          <t>凤霞 | 家珍 | 二喜 | 有庆 | 娘</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 二喜 | 地 | 病 | 穷</t>
+          <t>凤霞 | 二喜 | 家珍 | 穷</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4820,17 +4820,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>凤霞婚育身亡</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 二喜 | 地 | 死 | 田 | 干活 | 埋</t>
+          <t>凤霞 | 二喜 | 家珍 | 吃饭</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4859,17 +4859,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>凤霞 | 二喜 | 队长</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 队长 | 地 | 死 | 田 | 爹 | 干活</t>
+          <t>二喜 | 队长 | 凤霞 | 公社 | 文化大革命 | 爹 | 命 | 日子</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>队长</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>其他/未分类</t>
-        </is>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>队长 | 地 | 地主 | 走资派 | 田 | 干活 | 命</t>
+          <t>队长 | 地主 | 走资派 | 孩子 | 命</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4938,17 +4938,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>凤霞 | 春生 | 队长</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>队长 | 地 | 春生 | 凤霞 | 娘 | 田 | 走资派 | 命</t>
+          <t>队长 | 春生 | 娘 | 凤霞 | 走资派 | 命</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 春生</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 地 | 死 | 走资派 | 娘 | 县长</t>
+          <t>春生 | 家珍 | 走资派 | 县长 | 说话 | 娘</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5016,22 +5016,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 春生</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 死 | 命 | 凤霞 | 有庆 | 爹 | 娘</t>
+          <t>春生 | 家珍 | 命 | 活着 | 爹 | 娘 | 有庆 | 凤霞</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 二喜 | 春生</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>凤霞 | 二喜 | 家珍 | 死 | 爹 | 有庆 | 娘 | 田</t>
+          <t>二喜 | 凤霞 | 家珍 | 爹 | 娘 | 人民公社 | 公社 | 有庆</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 二喜</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>家庭生活</t>
-        </is>
-      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 哭 | 死 | 有庆 | 娘 | 爹</t>
+          <t>二喜 | 凤霞 | 家珍 | 娘 | 豆子 | 爹 | 有庆 | 孩子</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5135,17 +5135,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>有庆献血身亡</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>凤霞 | 二喜</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 地 | 医生 | 哭 | 生孩子 | 爹 | 苦</t>
+          <t>二喜 | 凤霞 | 孩子 | 生孩子 | 爹 | 命</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5175,22 +5175,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t>凤霞婚育身亡</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>凤霞 | 有庆 | 二喜</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 死 | 有庆 | 哭 | 地 | 生孩子 | 爹</t>
+          <t>二喜 | 凤霞 | 孩子 | 有庆 | 生孩子 | 回家 | 爹 | 血</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t>凤霞婚育身亡</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 二喜</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家庭生活</t>
-        </is>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 死 | 哭 | 地 | 娘 | 有庆</t>
+          <t>二喜 | 凤霞 | 家珍 | 娘 | 有庆 | 回家 | 爹</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5253,17 +5253,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>贫困生计 | 家珍病逝</t>
-        </is>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 死 | 地 | 埋 | 有庆 | 苦根</t>
+          <t>二喜 | 家珍 | 凤霞 | 孩子 | 有庆 | 爹 | 苦根 | 说话</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>家珍 | 死 | 凤霞 | 有庆 | 二喜 | 苦根 | 苦 | 娘</t>
+          <t>家珍 | 二喜 | 有庆 | 凤霞 | 苦根 | 说话 | 活下去 | 回家</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5331,22 +5331,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
+          <t>家珍患病离世</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>二喜 | 死 | 苦根 | 家珍 | 苦 | 田 | 地 | 干活</t>
+          <t>二喜 | 苦根 | 家珍 | 爹 | 娘</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
           <t>二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 苦 | 爹 | 哭 | 地 | 饿 | 娘</t>
+          <t>二喜 | 苦根 | 爹 | 孩子 | 饿 | 娘 | 命</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
           <t>凤霞 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 凤霞 | 苦 | 死 | 地 | 命 | 爹</t>
+          <t>二喜 | 苦根 | 凤霞 | 孩子 | 命 | 说话 | 爹 | 日子</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>二喜苦根悲剧</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>家珍 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 死 | 苦 | 水泥板 | 爹 | 命 | 家珍</t>
+          <t>二喜 | 苦根 | 水泥板 | 爹 | 命 | 日子 | 血 | 家珍</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>二喜苦根悲剧</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>死亡苦难 | 活着信念</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 死 | 苦 | 医院 | 地 | 爹 | 凤霞</t>
+          <t>二喜 | 苦根 | 爹 | 孩子 | 命 | 有庆 | 凤霞 | 一家人</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5526,17 +5526,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>苦根</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>苦根 | 苦 | 爹 | 地 | 田 | 娘 | 干活</t>
+          <t>苦根 | 爹 | 孩子 | 娘</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>二喜苦根悲剧</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>苦根 | 二喜 | 死 | 苦 | 爹 | 地 | 坟 | 哭</t>
+          <t>二喜 | 苦根 | 爹 | 孩子 | 娘 | 活着 | 日子</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞 | 二喜 | 苦根 | 队长</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>苦根 | 苦 | 地 | 队长 | 二喜 | 田 | 凤霞 | 娘</t>
+          <t>苦根 | 队长 | 孩子 | 二喜 | 说话 | 凤霞 | 娘 | 日子</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t>活着与生命态度</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>福贵 | 凤霞 | 苦根</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>苦根 | 苦 | 牛 | 买牛 | 凤霞 | 田 | 爹 | 娘</t>
+          <t>苦根 | 买牛 | 凤霞 | 说话 | 爹 | 娘 | 孩子 | 日子</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>福贵 | 苦根</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>苦根 | 苦 | 死 | 病 | 豆子 | 熬 | 田 | 地</t>
+          <t>苦根 | 豆子 | 熬 | 吃饭 | 回家 | 日子</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>二喜苦根悲剧</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>家珍 | 苦根 | 龙二 | 春生</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>死 | 苦根 | 苦 | 埋 | 命 | 豆子 | 龙二 | 家珍</t>
+          <t>苦根 | 命 | 豆子 | 龙二 | 孩子 | 日子 | 春生 | 家珍</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5760,22 +5760,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>赌博败家</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
           <t>苦根</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>贫困生计 | 活着信念</t>
-        </is>
-      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>牛 | 死 | 地 | 苦根 | 买牛 | 命 | 干活 | 老牛</t>
+          <t>买牛 | 命 | 苦根 | 老牛 | 牛市 | 说话 | 孩子 | 活着</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5800,17 +5800,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>福贵 | 家珍 | 凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>牛 | 二喜 | 干活 | 家珍 | 凤霞 | 有庆 | 苦根 | 爹</t>
+          <t>二喜 | 老牛 | 爹 | 有庆 | 凤霞 | 家珍 | 苦根 | 命</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>贫困生存压力</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
           <t>家珍 | 凤霞 | 有庆 | 二喜 | 苦根</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>贫困生计</t>
-        </is>
-      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>二喜 | 田 | 地 | 家珍 | 凤霞 | 有庆 | 苦根 | 牛</t>
+          <t>二喜 | 有庆 | 凤霞 | 家珍 | 苦根 | 孩子</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">

--- a/metadata_experiment/data/index_catalog.xlsx
+++ b/metadata_experiment/data/index_catalog.xlsx
@@ -484,13 +484,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>序言与创作背景</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>作家 | 写作 | 作者 | 作品 | 前言</t>
+          <t>作家 | 写作 | 前言 | 排版软件</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,13 +519,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>序言与创作背景</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>作家 | 作品 | 老黑奴 | 命</t>
+          <t>作家 | 死 | 老黑奴 | 民歌</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -554,13 +554,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>活着 | 老黑奴 | 娘 | 孩子 | 写作 | 作品</t>
+          <t>老黑奴 | 娘 | 民歌 | 田间 | 写作</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,13 +589,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孩子</t>
+          <t>庄稼 | 我遇到</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老牛 | 耕田 | 田地 | 命</t>
+          <t>老牛 | 我遇到</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>爹 | 耕田 | 二喜 | 田产 | 有庆 | 凤霞 | 家珍 | 苦根</t>
+          <t>凤霞 | 二喜 | 有庆 | 田产 | 娘 | 家珍 | 苦根 | 田间</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>爹 | 凤霞 | 田地 | 家珍 | 穷</t>
+          <t>凤霞 | 嫁 | 米 | 家珍</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>爹 | 赌博 | 有庆 | 凤霞 | 家珍 | 回家 | 娘 | 日子</t>
+          <t>凤霞 | 有庆 | 赌博 | 回家 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>爹 | 娘 | 赌博 | 有庆 | 家珍 | 凤霞 | 日子</t>
+          <t>凤霞 | 有庆 | 娘 | 病 | 赌博 | 家珍 | 米</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -825,12 +825,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>爹 | 回家</t>
+          <t>回家 | 米 | 病 | 死</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>家珍 | 娘 | 爹 | 日子</t>
+          <t>家珍 | 娘 | 死</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>龙二 | 爹 | 赌博 | 家珍 | 娘 | 骰子 | 凤霞 | 说话</t>
+          <t>龙二 | 凤霞 | 赌博 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>龙二 | 家珍 | 骰子 | 赌博 | 娘 | 有庆 | 说话</t>
+          <t>龙二 | 家珍 | 赌博 | 有庆 | 娘</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>家珍 | 龙二 | 爹 | 有庆 | 上学 | 说话</t>
+          <t>家珍 | 龙二 | 死 | 有庆 | 上学 | 米</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>龙二 | 骰子 | 家珍 | 有庆 | 上学 | 回家 | 娘 | 命</t>
+          <t>龙二 | 家珍 | 回家 | 有庆 | 米 | 上学 | 娘</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>龙二 | 输光 | 骰子 | 家产 | 穷</t>
+          <t>龙二 | 输光 | 死 | 家产 | 米</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>娘 | 爹 | 家珍 | 家产 | 输光 | 回家 | 有庆 | 穷</t>
+          <t>死 | 娘 | 回家 | 家珍 | 家产 | 输光 | 有庆</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>爹 | 娘 | 凤霞 | 家珍 | 说话 | 孩子 | 穷 | 命</t>
+          <t>凤霞 | 娘 | 家珍 | 死</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>爹 | 娘 | 命 | 穷</t>
+          <t>娘 | 死</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>爹 | 龙二 | 回家 | 凤霞 | 娘 | 血 | 家珍 | 没钱</t>
+          <t>凤霞 | 回家 | 死 | 龙二 | 血 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>徐家败落与父亲去世</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>爹 | 娘 | 家珍 | 凤霞 | 吃饭 | 回家 | 穷 | 没钱</t>
+          <t>凤霞 | 娘 | 回家 | 家珍</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>爹 | 龙二 | 娘</t>
+          <t>龙二 | 死 | 搬出 | 娘</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>徐家败落与父亲去世</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>爹 | 家珍 | 娘 | 凤霞 | 断气 | 命</t>
+          <t>凤霞 | 家珍 | 娘 | 死</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>家珍 | 爹 | 娘 | 凤霞 | 穷</t>
+          <t>家珍 | 死 | 凤霞 | 娘 | 嫁</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 娘 | 爹 | 孩子 | 命</t>
+          <t>凤霞 | 家珍 | 娘 | 死</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>凤霞 | 日子 | 老牛 | 爹</t>
+          <t>凤霞 | 讲述 | 老牛 | 我遇到</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>叙述者见闻</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 娘 | 爹 | 孩子</t>
+          <t>凤霞 | 娘 | 家珍 | 讲述</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>龙二 | 娘 | 凤霞 | 穷 | 地主 | 爹 | 日子</t>
+          <t>龙二 | 凤霞 | 娘 | 种地 | 地主</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>龙二 | 娘 | 血 | 凤霞 | 穷 | 一家人</t>
+          <t>龙二 | 凤霞 | 娘 | 血 | 死 | 病 | 庄稼 | 农活</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>徐家败落与父亲去世</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>娘 | 凤霞 | 日子 | 龙二 | 家产 | 输光 | 血 | 一辈子</t>
+          <t>凤霞 | 死 | 娘 | 龙二 | 血 | 病 | 家产 | 输光</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>徐家败落与父亲去世</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>龙二 | 凤霞 | 娘 | 日子 | 赌场 | 一辈子</t>
+          <t>凤霞 | 龙二 | 娘 | 死 | 赌场 | 种地</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>家珍 | 娘 | 龙二 | 有庆 | 凤霞 | 赌场 | 爹 | 孩子</t>
+          <t>凤霞 | 家珍 | 有庆 | 娘 | 龙二 | 赌场 | 种地</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>家珍 | 娘 | 凤霞 | 有庆 | 穷 | 孩子</t>
+          <t>凤霞 | 家珍 | 娘 | 有庆</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>家珍 | 娘 | 有庆 | 日子 | 凤霞 | 说话 | 爹 | 孩子</t>
+          <t>家珍 | 有庆 | 娘 | 凤霞 | 家珍回来 | 病</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 国民党 | 大炮 | 有庆 | 爹 | 娘 | 孩子</t>
+          <t>凤霞 | 死 | 有庆 | 家珍 | 家珍回来 | 大炮 | 国民党 | 娘</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1878,18 +1878,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>赌博败家</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>大炮 | 娘 | 壮丁 | 国民党 | 血</t>
+          <t>死 | 大炮 | 血 | 娘 | 壮丁 | 国民党</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>参军战争</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>老全 | 大炮 | 命 | 壮丁 | 当兵 | 田地 | 血 | 家珍</t>
+          <t>大炮 | 死 | 血 | 当兵 | 壮丁 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>老全 | 春生 | 大炮 | 娘 | 孩子 | 命</t>
+          <t>死 | 春生 | 大炮 | 娘</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>老全 | 命 | 春生 | 赌钱 | 解放军 | 粮食 | 血 | 说话</t>
+          <t>死 | 血 | 米 | 春生 | 赌钱 | 解放军 | 粮食</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>老全 | 娘 | 饿 | 命</t>
+          <t>死 | 米 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>其他/未分类</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>春生 | 老全 | 大炮 | 命 | 日子</t>
+          <t>春生 | 米 | 死 | 大炮</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>春生 | 老全 | 大炮 | 娘 | 孩子 | 饿 | 日子 | 一辈子</t>
+          <t>春生 | 死 | 大炮 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>说话 | 老全 | 春生 | 活着 | 有庆 | 凤霞 | 家珍 | 娘</t>
+          <t>死 | 凤霞 | 春生 | 有庆 | 娘 | 饿 | 家珍</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>老全 | 春生 | 血 | 说话 | 活着 | 命</t>
+          <t>死 | 血 | 春生</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>春生 | 老全 | 娘 | 家珍 | 孩子 | 命</t>
+          <t>死 | 春生 | 娘 | 米 | 家珍</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>解放军 | 春生 | 孩子 | 大炮 | 活着 | 命</t>
+          <t>死 | 解放军 | 春生 | 大炮</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>回家 | 解放军 | 饿 | 家珍 | 说话 | 娘 | 命</t>
+          <t>回家 | 解放军 | 死 | 饿 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>凤霞 | 有庆 | 解放军 | 家珍 | 爹 | 娘 | 饿</t>
+          <t>凤霞 | 有庆 | 解放军 | 死 | 家珍 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>家珍 | 娘 | 有庆 | 凤霞 | 龙二 | 爹 | 孩子 | 赌钱</t>
+          <t>凤霞 | 家珍 | 死 | 有庆 | 娘 | 龙二 | 回家 | 赌钱</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>土地改革与龙二</t>
+          <t>土地改革与龙二被枪决</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>龙二 | 地主 | 枪毙 | 五枪 | 田产 | 土地改革 | 家珍 | 回家</t>
+          <t>龙二 | 死 | 回家 | 地主 | 枪毙 | 五枪 | 田产 | 家珍</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>参军战争</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>龙二 | 家珍 | 命 | 战场 | 五枪 | 一家人 | 爹</t>
+          <t>死 | 龙二 | 家珍 | 战场 | 五枪 | 病 | 讲述</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 老牛 | 回家 | 饿 | 日子</t>
+          <t>凤霞 | 有庆 | 家珍 | 回家 | 饿 | 老牛</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 说话 | 上学 | 送人 | 娘 | 孩子</t>
+          <t>凤霞 | 家珍 | 有庆 | 死 | 送人 | 上学 | 娘</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 爹</t>
+          <t>凤霞 | 家珍 | 有庆</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>有庆 | 凤霞 | 家珍 | 上学 | 娘 | 吃饭 | 爹 | 日子</t>
+          <t>凤霞 | 有庆 | 家珍 | 上学 | 娘</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>上学 | 有庆 | 凤霞 | 孩子 | 家珍 | 吃饭 | 爹 | 娘</t>
+          <t>凤霞 | 有庆 | 上学 | 死 | 家珍 | 学校 | 娘</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 爹</t>
+          <t>凤霞 | 有庆 | 家珍</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 有庆 | 上学 | 孩子 | 吃饭 | 回家 | 娘</t>
+          <t>凤霞 | 家珍 | 有庆 | 死 | 回家 | 上学 | 娘 | 饿</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞回家与聋哑</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 上学 | 凤霞 | 孩子 | 回家 | 饿 | 吃饭</t>
+          <t>有庆 | 凤霞 | 死 | 家珍 | 上学 | 回家 | 饿 | 娘</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>队长 | 人民公社 | 公社 | 有庆 | 孩子 | 上学 | 家珍 | 当兵</t>
+          <t>有庆 | 队长 | 凤霞 | 公社 | 死 | 上学 | 学校 | 家珍</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>人民公社与大炼钢</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>食堂 | 队长 | 有庆 | 家珍 | 饿 | 人民公社 | 公社 | 凤霞</t>
+          <t>有庆 | 食堂 | 队长 | 凤霞 | 家珍 | 死 | 饿 | 米</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>人民公社与饥荒</t>
+          <t>人民公社与大炼钢</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>有庆 | 队长 | 公社 | 人民公社 | 挨饿 | 家珍 | 回家 | 孩子</t>
+          <t>有庆 | 凤霞 | 回家 | 队长 | 公社 | 家珍 | 上学 | 食堂</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>赌博败家</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>队长 | 家珍 | 家产 | 人民公社 | 公社 | 爹 | 日子</t>
+          <t>队长 | 家珍 | 家产 | 公社</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>人民公社与饥荒</t>
+          <t>徐家败落与父亲去世</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>队长 | 家珍 | 人民公社 | 公社 | 娘 | 食堂 | 一家人 | 吃饭</t>
+          <t>队长 | 家珍 | 死 | 娘 | 公社 | 食堂</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>队长 | 有庆 | 家珍 | 吃饭 | 娘 | 孩子</t>
+          <t>有庆 | 队长 | 死 | 家珍 | 病 | 娘</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 凤霞 | 日子 | 公社 | 食堂 | 有庆 | 孩子</t>
+          <t>家珍 | 凤霞 | 病 | 有庆 | 队长 | 嫁 | 医院 | 公社</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 凤霞 | 孩子 | 人民公社 | 公社 | 回家 | 爹</t>
+          <t>有庆 | 凤霞 | 家珍 | 回家 | 病 | 庄稼 | 公社</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 凤霞 | 孩子 | 人民公社 | 公社 | 回家</t>
+          <t>家珍 | 凤霞 | 有庆 | 回家 | 公社</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 凤霞 | 龙二 | 回家 | 软骨病 | 娘</t>
+          <t>凤霞 | 家珍 | 队长 | 病 | 回家 | 医院 | 龙二 | 医生</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 有庆 | 凤霞 | 食堂 | 软骨病 | 吃饭 | 回家</t>
+          <t>凤霞 | 家珍 | 队长 | 病 | 有庆 | 回家 | 嫁 | 医生</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>队长 | 家珍 | 有庆 | 食堂 | 粮食 | 凤霞 | 熬 | 公社</t>
+          <t>凤霞 | 有庆 | 队长 | 家珍 | 病 | 学校 | 食堂 | 粮食</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 凤霞 | 孩子 | 队长 | 血 | 回家 | 一辈子</t>
+          <t>有庆 | 家珍 | 凤霞 | 病 | 死 | 回家 | 血 | 医生</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>有庆 | 国民党 | 孩子 | 家珍 | 爹 | 说话 | 凤霞</t>
+          <t>有庆 | 凤霞 | 国民党 | 学校 | 家珍 | 死 | 病</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 说话 | 国民党 | 孩子 | 食堂 | 凤霞 | 送人</t>
+          <t>有庆 | 家珍 | 凤霞 | 死 | 回家 | 国民党 | 送人 | 学校</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>有庆 | 孩子 | 爹 | 家珍 | 跑步 | 回家 | 说话</t>
+          <t>有庆 | 学校 | 回家 | 家珍 | 跑步</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>有庆 | 孩子 | 爹 | 跑步 | 回家</t>
+          <t>有庆 | 回家 | 跑步</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>有庆 | 跑步 | 凤霞 | 家珍 | 回家 | 爹 | 娘</t>
+          <t>有庆 | 凤霞 | 回家 | 跑步 | 学校 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>饥荒与借粮求生</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>粮食 | 有庆 | 队长 | 家珍 | 饿 | 孩子 | 熬 | 公社</t>
+          <t>死 | 有庆 | 粮食 | 米 | 队长 | 饿 | 家珍 | 公社</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>有庆上学与跑步</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 爹 | 孩子 | 挨饿 | 娘 | 饿 | 粮食</t>
+          <t>有庆 | 家珍 | 娘 | 饿 | 米 | 学校 | 粮食</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>有庆 | 爹 | 家珍 | 回家 | 孩子 | 命</t>
+          <t>有庆 | 米 | 回家 | 家珍</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>饥荒与借粮求生</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 队长 | 粮食 | 挨饿 | 饿 | 日子 | 凤霞</t>
+          <t>有庆 | 家珍 | 死 | 米 | 凤霞 | 队长 | 粮食 | 病</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>凤霞 | 饿 | 有庆 | 说话 | 家珍 | 壮丁 | 田地 | 爹</t>
+          <t>凤霞 | 有庆 | 饿 | 家珍 | 壮丁 | 娘</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>凤霞婚育身亡</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>队长 | 凤霞 | 命 | 家珍 | 一家人 | 说话 | 爹 | 娘</t>
+          <t>凤霞 | 队长 | 死 | 娘 | 家珍</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 有庆 | 爹 | 一家人 | 回家 | 命 | 孩子</t>
+          <t>凤霞 | 有庆 | 家珍 | 米 | 回家</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 有庆 | 说话 | 熬 | 凤霞 | 一家人 | 爹</t>
+          <t>有庆 | 米 | 家珍 | 队长 | 凤霞</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 凤霞 | 日子 | 说话 | 熬 | 有庆 | 血</t>
+          <t>家珍 | 凤霞 | 队长 | 米 | 血 | 有庆 | 娘 | 病</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 凤霞 | 身子 | 活着 | 日子</t>
+          <t>死 | 凤霞 | 家珍 | 有庆 | 病</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>血 | 有庆 | 孩子 | 献血 | 血型 | 县长 | 家珍 | 命</t>
+          <t>血 | 有庆 | 医院 | 学校 | 献血 | 医生 | 县长 | 家珍</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>有庆 | 血 | 抽血 | 孩子 | 县长 | 爹 | 上学 | 血型</t>
+          <t>有庆 | 血 | 死 | 医生 | 医院 | 抽血 | 县长 | 上学</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>有庆 | 活着 | 上学 | 抽血 | 血 | 家珍</t>
+          <t>有庆 | 死 | 医生 | 血 | 上学 | 抽血 | 医院 | 家珍</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>春生文革与自杀</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>县长 | 春生 | 有庆 | 老全 | 命 | 抽血 | 血</t>
+          <t>死 | 县长 | 春生 | 有庆 | 医生 | 血 | 抽血 | 病</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>春生 | 有庆 | 家珍 | 老全 | 爹 | 娘 | 上学 | 说话</t>
+          <t>有庆 | 死 | 春生 | 家珍 | 娘 | 上学 | 病</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>家珍患病离世</t>
+          <t>有庆献血死亡</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>有庆 | 家珍 | 说话 | 日子 | 上学 | 凤霞 | 爹 | 娘</t>
+          <t>有庆 | 家珍 | 死 | 凤霞 | 医院 | 上学 | 娘 | 病</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 凤霞 | 说话 | 娘 | 活着 | 日子</t>
+          <t>有庆 | 家珍 | 死 | 凤霞 | 娘</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>家珍 | 有庆 | 做人 | 田地 | 耕田 | 说话</t>
+          <t>有庆 | 家珍 | 死 | 庄稼 | 讲述</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>家珍 | 队长 | 说话 | 日子 | 公社 | 有庆 | 凤霞 | 软骨病</t>
+          <t>家珍 | 医生 | 凤霞 | 死 | 有庆 | 队长 | 病 | 公社</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 队长 | 有庆 | 娘 | 穷 | 日子 | 吃饭</t>
+          <t>凤霞 | 家珍 | 死 | 有庆 | 队长 | 嫁 | 娘 | 病</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 娘 | 有庆 | 回家 | 说话 | 饿 | 熬</t>
+          <t>凤霞 | 家珍 | 死 | 病 | 回家 | 有庆 | 娘 | 医生</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>家珍患病离世</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 队长 | 有庆 | 县长 | 凤霞 | 解放军 | 回家</t>
+          <t>春生 | 家珍 | 死 | 凤霞 | 有庆 | 队长 | 县长 | 病</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>家珍 | 凤霞 | 春生 | 队长 | 娘 | 命 | 文化大革命</t>
+          <t>凤霞 | 家珍 | 春生 | 死 | 队长 | 娘 | 嫁 | 病</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>娘 | 凤霞 | 命</t>
+          <t>凤霞 | 娘 | 嫁</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>凤霞 | 队长 | 家珍 | 二喜 | 说话 | 娘 | 做人</t>
+          <t>凤霞 | 死 | 队长 | 家珍 | 嫁 | 二喜 | 娘</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>家珍 | 二喜 | 队长 | 凤霞 | 娘 | 说话 | 爹 | 穷</t>
+          <t>凤霞 | 家珍 | 二喜 | 队长 | 死 | 娘 | 送走 | 相亲</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 穷 | 凤霞 | 队长 | 耕田 | 说话</t>
+          <t>二喜 | 凤霞 | 家珍 | 嫁 | 相亲 | 队长</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 吃饭 | 穷</t>
+          <t>二喜 | 凤霞 | 家珍</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 爹 | 娘 | 说话 | 命</t>
+          <t>凤霞 | 二喜 | 家珍 | 娘</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>家庭日常生活</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 送人 | 爹 | 娘 | 孩子</t>
+          <t>凤霞 | 二喜 | 家珍 | 嫁 | 送人 | 娘</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>凤霞婚育身亡</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 娘 | 爹</t>
+          <t>凤霞 | 二喜 | 家珍 | 嫁 | 娘</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>凤霞 | 家珍 | 二喜 | 有庆 | 娘</t>
+          <t>凤霞 | 家珍 | 二喜 | 有庆 | 嫁 | 娘</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>凤霞 | 二喜 | 家珍 | 穷</t>
+          <t>凤霞 | 二喜 | 家珍 | 嫁 | 病</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>凤霞婚育身亡</t>
+          <t>凤霞被送走</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>凤霞 | 二喜 | 家珍 | 吃饭</t>
+          <t>凤霞 | 二喜 | 家珍 | 死</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>二喜 | 队长 | 凤霞 | 公社 | 文化大革命 | 爹 | 命 | 日子</t>
+          <t>凤霞 | 二喜 | 队长 | 死 | 公社</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>其他/未分类</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>队长 | 地主 | 走资派 | 孩子 | 命</t>
+          <t>队长 | 地主 | 走资派</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>春生与文化大革命</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>队长 | 春生 | 娘 | 凤霞 | 走资派 | 命</t>
+          <t>队长 | 春生 | 凤霞 | 娘 | 走资派</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 走资派 | 县长 | 说话 | 娘</t>
+          <t>春生 | 家珍 | 死 | 走资派 | 娘 | 县长</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>参军战争</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>春生 | 家珍 | 命 | 活着 | 爹 | 娘 | 有庆 | 凤霞</t>
+          <t>春生 | 死 | 家珍 | 凤霞 | 有庆 | 娘 | 县长</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 爹 | 娘 | 人民公社 | 公社 | 有庆</t>
+          <t>凤霞 | 二喜 | 家珍 | 死 | 有庆 | 娘 | 嫁 | 公社</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>凤霞婚姻</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 娘 | 豆子 | 爹 | 有庆 | 孩子</t>
+          <t>凤霞 | 二喜 | 家珍 | 死 | 有庆 | 娘 | 豆子</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>有庆献血身亡</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 孩子 | 生孩子 | 爹 | 命</t>
+          <t>凤霞 | 二喜 | 医生 | 生孩子</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>凤霞婚育身亡</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 孩子 | 有庆 | 生孩子 | 回家 | 爹 | 血</t>
+          <t>凤霞 | 二喜 | 死 | 有庆 | 回家 | 生孩子 | 血 | 医生</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>凤霞婚育身亡</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>二喜 | 凤霞 | 家珍 | 娘 | 有庆 | 回家 | 爹</t>
+          <t>凤霞 | 二喜 | 死 | 家珍 | 娘 | 回家 | 有庆</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>家珍患病离世</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>二喜 | 家珍 | 凤霞 | 孩子 | 有庆 | 爹 | 苦根 | 说话</t>
+          <t>凤霞 | 死 | 二喜 | 家珍 | 有庆 | 医院 | 娘 | 苦根</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>家珍 | 二喜 | 有庆 | 凤霞 | 苦根 | 说话 | 活下去 | 回家</t>
+          <t>死 | 凤霞 | 家珍 | 有庆 | 回家 | 二喜 | 苦根 | 娘</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 家珍 | 爹 | 娘</t>
+          <t>死 | 二喜 | 苦根 | 家珍 | 娘</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>苦根死亡</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 爹 | 孩子 | 饿 | 娘 | 命</t>
+          <t>二喜 | 苦根 | 饿 | 娘</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>凤霞生产死亡</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 凤霞 | 孩子 | 命 | 说话 | 爹 | 日子</t>
+          <t>凤霞 | 二喜 | 苦根 | 死</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>二喜苦根悲剧</t>
+          <t>二喜意外死亡</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 水泥板 | 爹 | 命 | 日子 | 血 | 家珍</t>
+          <t>二喜 | 死 | 苦根 | 水泥板 | 血 | 医院 | 家珍</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>二喜苦根悲剧</t>
+          <t>二喜意外死亡</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 爹 | 孩子 | 命 | 有庆 | 凤霞 | 一家人</t>
+          <t>死 | 二喜 | 苦根 | 医院 | 凤霞 | 有庆 | 娘</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>苦根死亡</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>苦根 | 爹 | 孩子 | 娘</t>
+          <t>苦根 | 娘</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>二喜苦根悲剧</t>
+          <t>苦根死亡</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>二喜 | 苦根 | 爹 | 孩子 | 娘 | 活着 | 日子</t>
+          <t>死 | 二喜 | 苦根 | 爹死了 | 娘</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>苦根 | 队长 | 孩子 | 二喜 | 说话 | 凤霞 | 娘 | 日子</t>
+          <t>苦根 | 凤霞 | 队长 | 二喜 | 娘</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>活着与生命态度</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>苦根 | 买牛 | 凤霞 | 说话 | 爹 | 娘 | 孩子 | 日子</t>
+          <t>苦根 | 凤霞 | 买牛 | 娘</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>苦根死亡</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>苦根 | 豆子 | 熬 | 吃饭 | 回家 | 日子</t>
+          <t>苦根 | 死 | 豆子 | 回家 | 病</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>二喜苦根悲剧</t>
+          <t>苦根死亡</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>苦根 | 命 | 豆子 | 龙二 | 孩子 | 日子 | 春生 | 家珍</t>
+          <t>死 | 苦根 | 豆子 | 龙二 | 饿 | 春生 | 家珍 | 撑死</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>赌博败家</t>
+          <t>老牛与晚年</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>买牛 | 命 | 苦根 | 老牛 | 牛市 | 说话 | 孩子 | 活着</t>
+          <t>死 | 买牛 | 苦根 | 老牛</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>老牛与晚年</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>二喜 | 老牛 | 爹 | 有庆 | 凤霞 | 家珍 | 苦根 | 命</t>
+          <t>凤霞 | 死 | 二喜 | 有庆 | 老牛 | 家珍 | 苦根</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>贫困生存压力</t>
+          <t>租田务农与求生</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>二喜 | 有庆 | 凤霞 | 家珍 | 苦根 | 孩子</t>
+          <t>凤霞 | 二喜 | 有庆 | 家珍 | 苦根</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
